--- a/output7/【河洛白話注音-雅俗通】《尚有力量的每日祈禱文》.xlsx
+++ b/output7/【河洛白話注音-雅俗通】《尚有力量的每日祈禱文》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{002524FC-6EB9-40DF-8062-89B4AD1EA001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DB340F6-9400-4E81-B8B3-7A2423BE60D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="10" r:id="rId1"/>

--- a/output7/【河洛白話注音-雅俗通】《尚有力量的每日祈禱文》.xlsx
+++ b/output7/【河洛白話注音-雅俗通】《尚有力量的每日祈禱文》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DB340F6-9400-4E81-B8B3-7A2423BE60D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B7F6E3-E979-4E68-994B-3379BE6ED713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="10" r:id="rId1"/>

--- a/output7/【河洛白話注音-雅俗通】《尚有力量的每日祈禱文》.xlsx
+++ b/output7/【河洛白話注音-雅俗通】《尚有力量的每日祈禱文》.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B7F6E3-E979-4E68-994B-3379BE6ED713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B78A9C4-C535-4372-AECD-25BBC90EF0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
@@ -6722,7 +6722,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="7">
+  <dataValidations disablePrompts="1" count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8" xr:uid="{DE2F131F-8109-4114-9E19-8669EDE792F8}">
       <formula1>"TRUE, FALSE"</formula1>
     </dataValidation>

--- a/output7/【河洛白話注音-雅俗通】《尚有力量的每日祈禱文》.xlsx
+++ b/output7/【河洛白話注音-雅俗通】《尚有力量的每日祈禱文》.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B78A9C4-C535-4372-AECD-25BBC90EF0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{483A5A3A-DDB6-4FB9-AA8F-78851E999CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
